--- a/Test-Cases-and-Bug-Reports.xlsx
+++ b/Test-Cases-and-Bug-Reports.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13392" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13392" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Use Case 1" sheetId="1" r:id="rId1"/>
@@ -99,9 +99,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Use case 1: Testing the article</t>
-  </si>
-  <si>
     <t>Verify hyperlink on the article</t>
   </si>
   <si>
@@ -430,6 +427,9 @@
   </si>
   <si>
     <t>no preconditions</t>
+  </si>
+  <si>
+    <t>Use case 2: Testing the article</t>
   </si>
 </sst>
 </file>
@@ -603,6 +603,33 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -614,33 +641,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -936,31 +936,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="A1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -979,232 +979,232 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="A4" s="8">
         <v>101</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>102</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>103</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>104</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>102</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>103</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="E7" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="17" t="s">
+      <c r="F7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>105</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>106</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>104</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>105</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>106</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>107</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="17" t="s">
+      <c r="E10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>107</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>108</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>108</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="17" t="s">
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>109</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>109</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="17" t="s">
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>110</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
-        <v>110</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>9</v>
-      </c>
       <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="8">
         <v>111</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="B14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="D14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="6"/>
@@ -1237,31 +1237,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="A1" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>1</v>
@@ -1283,20 +1283,20 @@
       <c r="A4" s="4">
         <v>201</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="B4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>39</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1304,19 +1304,19 @@
       <c r="A5" s="4">
         <v>202</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="4"/>
@@ -1325,19 +1325,19 @@
       <c r="A6" s="4">
         <v>203</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="4"/>
@@ -1346,19 +1346,19 @@
       <c r="A7" s="4">
         <v>204</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="4"/>
@@ -1367,19 +1367,19 @@
       <c r="A8" s="4">
         <v>205</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="4"/>
@@ -1413,28 +1413,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1466,307 +1466,307 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="8">
+        <v>202</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="8"/>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="12">
-        <v>202</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B5" s="8">
+        <v>203</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="8">
+        <v>204</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="8">
+        <v>205</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:9" ht="229.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="8">
+        <v>103</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="8">
+        <v>106</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="8">
+        <v>107</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="8">
+        <v>108</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="8">
+        <v>109</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="12">
-        <v>203</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="19" t="s">
+      <c r="D12" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="8">
+        <v>110</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="12">
-        <v>204</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="12">
-        <v>205</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" ht="229.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="12">
-        <v>103</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="12">
-        <v>106</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="12">
-        <v>107</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="12">
-        <v>108</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="12">
-        <v>109</v>
-      </c>
-      <c r="C12" s="18" t="s">
+      <c r="D13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="8">
+        <v>111</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D14" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="12">
-        <v>110</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="E14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="12">
-        <v>111</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="12" t="s">
+      <c r="H14" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="12"/>
+      <c r="I14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
